--- a/Rental_prop_proforma.xlsx
+++ b/Rental_prop_proforma.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="smNativeData" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <fileSharing readOnlyRecommended="0" userName="jsrd"/>
   <workbookPr/>
@@ -14,22 +14,22 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <ns2:revision day="1775267756" val="1230" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <ns2:docPrefs id="1775267756" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <ns2:compatibility id="1775267756" overlapCells="1"/>
-      <ns2:defCurrency id="1775267756"/>
+      <pm:revision xmlns:pm="smNativeData" day="1775607099" val="1230" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1775607099" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1775607099" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1775607099"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
   <si>
     <t>APM RENTAL PROPERTY DEAL ANALYZER</t>
   </si>
   <si>
-    <t>Green Cells- you can edit and customize. Yellos are calculated cells</t>
+    <t>Green Cells- you can edit and customize. Yellows are calculated cells</t>
   </si>
   <si>
     <t>PROPERTY DETAILS</t>
@@ -116,6 +116,9 @@
     <t>Title, fees, stamps</t>
   </si>
   <si>
+    <t>Editable</t>
+  </si>
+  <si>
     <t>ANNUAL EXPENSES</t>
   </si>
   <si>
@@ -203,6 +206,15 @@
     <t>Quick read</t>
   </si>
   <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Quick read</t>
+  </si>
+  <si>
     <t>Monthly LOC Payment</t>
   </si>
   <si>
@@ -233,7 +245,7 @@
     <t>DSCR</t>
   </si>
   <si>
-    <t>Debt covge Serv Ratio</t>
+    <t>Debt service coverage</t>
   </si>
   <si>
     <t>LTV</t>
@@ -308,48 +320,87 @@
     <t>KEY PERFORMANCE METRICS</t>
   </si>
   <si>
+    <t>DSCR detail (lender view)</t>
+  </si>
+  <si>
     <t>Net Operating Income (NOI)</t>
   </si>
   <si>
     <t>Rent after annual vacancy minus operating expenses (before debt)</t>
   </si>
   <si>
+    <t>Annual debt service (total)</t>
+  </si>
+  <si>
+    <t>Cap Rate</t>
+  </si>
+  <si>
     <t>NOI/Price. 5-10% typical</t>
   </si>
   <si>
+    <t>DSCR (mortgage only)</t>
+  </si>
+  <si>
     <t>Cash-on-Cash Return</t>
   </si>
   <si>
     <t>Annual cash flow after debt divided by total cash invested</t>
   </si>
   <si>
+    <t>Year 1 DSCR (projection)</t>
+  </si>
+  <si>
     <t>Gross Rent Multiplier</t>
   </si>
   <si>
     <t>Price/Annual Rent. Lower=better</t>
   </si>
   <si>
+    <t>Cushion vs 1.25 (total DSCR)</t>
+  </si>
+  <si>
     <t>1% Rule Test</t>
   </si>
   <si>
     <t>Monthly Rent / Price. &gt;=1% passes</t>
   </si>
   <si>
+    <t>Meets typical 1.25 test?</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
     <t>Target &gt;= 1.20; lower values mean tighter debt coverage</t>
   </si>
   <si>
+    <t>LTV</t>
+  </si>
+  <si>
     <t>Loan-to-value. Lower is safer and more financeable</t>
   </si>
   <si>
+    <t>Rent allocation (annual)</t>
+  </si>
+  <si>
     <t>Operating Expense Ratio</t>
   </si>
   <si>
     <t>Operating expenses as a share of effective rent</t>
   </si>
   <si>
+    <t>Operating expenses</t>
+  </si>
+  <si>
+    <t>Debt service</t>
+  </si>
+  <si>
     <t>BREAKEVEN ANALYSIS</t>
   </si>
   <si>
+    <t>Cash after debt</t>
+  </si>
+  <si>
     <t>Max Monthly Payment</t>
   </si>
   <si>
@@ -485,6 +536,9 @@
     <t>Year 1 Total</t>
   </si>
   <si>
+    <t>Other opex (ins+tax) — chart helper</t>
+  </si>
+  <si>
     <t>Proforma Review – Long-Term Rental Template</t>
   </si>
   <si>
@@ -494,6 +548,9 @@
     <t>Current snapshot from model</t>
   </si>
   <si>
+    <t>Cap Rate</t>
+  </si>
+  <si>
     <t>Target often 5%–10%+</t>
   </si>
   <si>
@@ -503,15 +560,33 @@
     <t>Review</t>
   </si>
   <si>
+    <t>Cash-on-Cash Return</t>
+  </si>
+  <si>
     <t>Target often 8%–12%+</t>
   </si>
   <si>
+    <t>Strong on paper</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
     <t>Lenders often want ≥1.20</t>
   </si>
   <si>
     <t>Pass</t>
   </si>
   <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>LTV</t>
+  </si>
+  <si>
     <t>Conventional investor loans often ≤75%–80%</t>
   </si>
   <si>
@@ -530,6 +605,9 @@
     <t>Negative in model</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -572,6 +650,9 @@
     <t>Add lender-ready assumptions for down payment %, origination points, reserves, and loan fees. Highlight LTV above 80% with a warning.</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Operating expenses</t>
   </si>
   <si>
@@ -584,6 +665,9 @@
     <t>Expand operating expenses and allow both fixed-dollar and % of rent assumptions. A vacancy line is especially important for long-term rentals.</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Debt presentation</t>
   </si>
   <si>
@@ -596,6 +680,9 @@
     <t>Add an amortization schedule with beginning balance, interest, principal, ending balance, and cumulative principal paid.</t>
   </si>
   <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>Tax section</t>
   </si>
   <si>
@@ -608,6 +695,9 @@
     <t>Rename to Taxable Income/(Loss) and Tax Impact, or reverse the sign convention so benefits display as positive savings only when applicable.</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Exit analysis</t>
   </si>
   <si>
@@ -620,6 +710,9 @@
     <t>Add an exit section with sale price growth, selling costs, loan payoff, net sale proceeds, IRR, and equity multiple.</t>
   </si>
   <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>Sensitivity / scenarios</t>
   </si>
   <si>
@@ -630,6 +723,9 @@
   </si>
   <si>
     <t>Add best/base/worst case scenarios and a 2-way sensitivity table for rent vs purchase price or rent vs interest rate.</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
   <si>
     <t>Visual design</t>
@@ -660,23 +756,23 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0\ _$_-;\-* #,##0\ _$_-;_-* &quot;-&quot;\ _$_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;$&quot;_-;\-* #,##0.00\ &quot;$&quot;_-;_-* &quot;-&quot;??\ &quot;$&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _$_-;\-* #,##0.00\ _$_-;_-* &quot;-&quot;??\ _$_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(_$* #,##0.00_);_(_$* \(#,##0.00\);_(_$* &quot;-&quot;????_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(_$* #,##0_);_(_$* \(#,##0\);_(_$* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;????_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.00_);([$$-409]#,##0.00)"/>
+    <numFmt numFmtId="170" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="9" formatCode="0%"/>
     <numFmt numFmtId="2" formatCode="0.00"/>
     <numFmt numFmtId="49" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="_(_$* #,##0.00_);_(_$* \(#,##0.00\);_(_$* &quot;-&quot;????_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(_$* #,##0_);_(_$* \(#,##0\);_(_$* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;????_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="9" formatCode="0%"/>
+    <numFmt numFmtId="10" formatCode="0.00%"/>
     <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="[$$-409]#,##0.00_);([$$-409]#,##0.00)"/>
-    <numFmt numFmtId="172" formatCode="$#,##0.00"/>
     <numFmt numFmtId="1" formatCode="0"/>
-    <numFmt numFmtId="10" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -684,7 +780,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -699,7 +795,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -715,7 +811,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="0B1D3A" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="0B1D3A" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -730,7 +826,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -746,7 +842,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="666666" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="666666" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" i="1"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" i="1"/>
             <pm:ea face="SimSun" sz="200" lang="default" i="1"/>
@@ -762,7 +858,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -777,7 +873,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="999999" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="999999" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -793,7 +889,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="333333" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="333333" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -808,7 +904,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="0000FF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="0000FF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -823,7 +919,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="1D4ED8" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="1D4ED8" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -839,7 +935,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="666666" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="666666" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="180" lang="default" i="1"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" i="1"/>
             <pm:ea face="SimSun" sz="180" lang="default" i="1"/>
@@ -855,7 +951,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -871,7 +967,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="1F1F1F" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="1F1F1F" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -887,7 +983,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="123B6D" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="123B6D" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -902,7 +998,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="1F1F1F" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="1F1F1F" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -918,7 +1014,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -934,7 +1030,7 @@
       <sz val="16"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="320" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="320" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="320" lang="default" weight="bold"/>
@@ -950,7 +1046,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="1F2937" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="1F2937" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" i="1"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" i="1"/>
             <pm:ea face="SimSun" sz="220" lang="default" i="1"/>
@@ -966,7 +1062,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="0F2747" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="0F2747" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -982,7 +1078,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="7C2D12" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="7C2D12" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -998,7 +1094,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="123B6D" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="123B6D" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -1006,8 +1102,73 @@
         </ext>
       </extLst>
     </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="12"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="666666" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="240" lang="default" weight="bold" i="1"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default" i="1"/>
+            <pm:ea face="SimSun" sz="200" lang="default" i="1"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="240" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775607099" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="240" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1020,7 +1181,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="000B1F44" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="000B1F44" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1031,7 +1192,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00FFFDEB" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFFDEB" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1042,7 +1203,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00123B6D" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00123B6D" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1053,7 +1214,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1064,7 +1225,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00F7FBFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00F7FBFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1075,7 +1236,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1086,7 +1247,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00F3F7FB" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00F3F7FB" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1097,7 +1258,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="001F5A99" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="001F5A99" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1111,7 +1272,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="000F2747" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="000F2747" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1122,7 +1283,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00EAF2F8" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00EAF2F8" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1133,7 +1294,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00D9EAF7" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00D9EAF7" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1144,7 +1305,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00FFF7ED" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFF7ED" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1155,7 +1316,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1166,7 +1327,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00E7F3EA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00E7F3EA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1177,7 +1338,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00D9E6F2" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00D9E6F2" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1188,7 +1349,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00E8F1EA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00E8F1EA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1199,7 +1360,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="009EFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="009EFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1210,7 +1371,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="009EFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="009EFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1221,7 +1382,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1232,7 +1393,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1243,7 +1404,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFFF9E" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1254,7 +1415,24 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFFF9E" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00E2EFDA" bgLvl="0" bgClr="00E2EFDA"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1265,13 +1443,13 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="28">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -1287,7 +1465,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1306,7 +1484,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1325,7 +1503,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1344,7 +1522,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1363,7 +1541,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1382,7 +1560,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
@@ -1406,7 +1584,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1425,7 +1603,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
@@ -1449,7 +1627,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1468,7 +1646,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
@@ -1492,7 +1670,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1511,7 +1689,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1530,7 +1708,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1549,7 +1727,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1568,7 +1746,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1587,7 +1765,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1606,7 +1784,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
@@ -1630,7 +1808,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D1D5DB"/>
@@ -1654,7 +1832,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
@@ -1678,7 +1856,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1697,7 +1875,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
@@ -1721,7 +1899,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1740,7 +1918,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
@@ -1759,7 +1937,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="CCCCCC"/>
@@ -1775,33 +1953,97 @@
       <right style="none">
         <color rgb="FF000000"/>
       </right>
-      <top style="none">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="none">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775267756"/>
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1775607099">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1775607099"/>
         </ext>
       </extLst>
     </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1828,7 +2070,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1843,7 +2085,7 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1882,9 +2124,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1897,7 +2139,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1906,46 +2148,34 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1955,7 +2185,7 @@
     <xf numFmtId="0" fontId="15" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="15" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1967,48 +2197,48 @@
     <xf numFmtId="1" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="10" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="9" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="9" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2020,7 +2250,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="9" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2028,18 +2258,28 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="8" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="23" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="23" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="24" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="24" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="26" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -2049,14 +2289,86 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7" customBuiltin="1"/>
     <cellStyle name="Percent" xfId="5" builtinId="5" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00C6EFCE"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00FFEB9C"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00C6EFCE"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00FFEB9C"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
         <color rgb="FF991B1B"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="991B1B">
+            <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="991B1B">
               <pm:latin weight="bold"/>
               <pm:cs weight="bold"/>
               <pm:ea weight="bold"/>
@@ -2069,7 +2381,7 @@
           <bgColor rgb="FFFECACA"/>
           <extLst>
             <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FECACA"/>
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FECACA"/>
             </ext>
           </extLst>
         </patternFill>
@@ -2081,7 +2393,7 @@
         <color rgb="FF92400E"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="92400E">
+            <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="92400E">
               <pm:latin weight="bold"/>
               <pm:cs weight="bold"/>
               <pm:ea weight="bold"/>
@@ -2094,7 +2406,7 @@
           <bgColor rgb="FFFEF3C7"/>
           <extLst>
             <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FEF3C7"/>
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FEF3C7"/>
             </ext>
           </extLst>
         </patternFill>
@@ -2106,7 +2418,7 @@
         <color rgb="FF166534"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1775267756" fgClr="166534">
+            <pm:charSpec xmlns:pm="smNativeData" id="1775607099" fgClr="166534">
               <pm:latin weight="bold"/>
               <pm:cs weight="bold"/>
               <pm:ea weight="bold"/>
@@ -2119,7 +2431,7 @@
           <bgColor rgb="FFDCFCE7"/>
           <extLst>
             <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1775267756" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00DCFCE7"/>
+              <pm:shade xmlns:pm="smNativeData" id="1775607099" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00DCFCE7"/>
             </ext>
           </extLst>
         </patternFill>
@@ -2129,10 +2441,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1775267756" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1775607099" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1775267756" count="32">
+      <pm:colors xmlns:pm="smNativeData" id="1775607099" count="33">
         <pm:color name="Color 24" rgb="0B1D3A"/>
         <pm:color name="Color 25" rgb="1D4ED8"/>
         <pm:color name="Color 26" rgb="1F1F1F"/>
@@ -2141,30 +2453,31 @@
         <pm:color name="Color 29" rgb="0F2747"/>
         <pm:color name="Color 30" rgb="7C2D12"/>
         <pm:color name="Color 31" rgb="0B1F44"/>
-        <pm:color name="Color 32" rgb="FFFFF0"/>
-        <pm:color name="Color 33" rgb="FFFDEB"/>
-        <pm:color name="Color 34" rgb="DCE6F1"/>
-        <pm:color name="Color 35" rgb="E7F3EA"/>
-        <pm:color name="Color 36" rgb="F7FBFF"/>
-        <pm:color name="Color 37" rgb="F3F7FB"/>
-        <pm:color name="Color 38" rgb="1F5A99"/>
-        <pm:color name="Color 39" rgb="EAF2F8"/>
-        <pm:color name="Color 40" rgb="D9EAF7"/>
-        <pm:color name="Color 41" rgb="FFF7ED"/>
-        <pm:color name="Color 42" rgb="D4EDDA"/>
-        <pm:color name="Color 43" rgb="D9E6F2"/>
-        <pm:color name="Color 44" rgb="E8F1EA"/>
-        <pm:color name="Color 45" rgb="9EFF9E"/>
-        <pm:color name="Color 46" rgb="9EFFFF"/>
-        <pm:color name="Color 47" rgb="3DFF3D"/>
-        <pm:color name="Color 48" rgb="D1D5DB"/>
-        <pm:color name="Color 49" rgb="991B1B"/>
-        <pm:color name="Color 50" rgb="FECACA"/>
-        <pm:color name="Color 51" rgb="92400E"/>
-        <pm:color name="Color 52" rgb="FEF3C7"/>
-        <pm:color name="Color 53" rgb="166534"/>
-        <pm:color name="Color 54" rgb="DCFCE7"/>
-        <pm:color name="Color 55" rgb="FFFF9E"/>
+        <pm:color name="Color 32" rgb="FFFDEB"/>
+        <pm:color name="Color 33" rgb="DCE6F1"/>
+        <pm:color name="Color 34" rgb="F7FBFF"/>
+        <pm:color name="Color 35" rgb="F3F7FB"/>
+        <pm:color name="Color 36" rgb="1F5A99"/>
+        <pm:color name="Color 37" rgb="EAF2F8"/>
+        <pm:color name="Color 38" rgb="D9EAF7"/>
+        <pm:color name="Color 39" rgb="FFF7ED"/>
+        <pm:color name="Color 40" rgb="E7F3EA"/>
+        <pm:color name="Color 41" rgb="D9E6F2"/>
+        <pm:color name="Color 42" rgb="E8F1EA"/>
+        <pm:color name="Color 43" rgb="9EFFFF"/>
+        <pm:color name="Color 44" rgb="9EFF9E"/>
+        <pm:color name="Color 45" rgb="FFFF9E"/>
+        <pm:color name="Color 46" rgb="E2EFDA"/>
+        <pm:color name="Color 47" rgb="D1D5DB"/>
+        <pm:color name="Color 48" rgb="991B1B"/>
+        <pm:color name="Color 49" rgb="FECACA"/>
+        <pm:color name="Color 50" rgb="92400E"/>
+        <pm:color name="Color 51" rgb="FEF3C7"/>
+        <pm:color name="Color 52" rgb="166534"/>
+        <pm:color name="Color 53" rgb="DCFCE7"/>
+        <pm:color name="Color 54" rgb="C6EFCE"/>
+        <pm:color name="Color 55" rgb="FFEB9C"/>
+        <pm:color name="Color 56" rgb="FFC7CE"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -2177,419 +2490,25 @@
   <c:roundedCorners val="0"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
-    <c:view3D>
-      <c:rotX val="15"/>
-      <c:rotY val="20"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="0"/>
-      <c:perspective val="30"/>
-    </c:view3D>
-    <c:floor>
-      <c:spPr/>
-    </c:floor>
-    <c:sideWall>
-      <c:spPr/>
-    </c:sideWall>
-    <c:backWall>
-      <c:spPr/>
-    </c:backWall>
     <c:plotArea>
       <c:layout/>
-      <c:bar3DChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Rent Collected</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t">
-                <a:rot lat="0" lon="0" rev="12000000"/>
-              </a:lightRig>
-            </a:scene3d>
-            <a:sp3d prstMaterial="warmMatte"/>
-          </c:spPr>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="9525">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Deal Analyzer'!$A$105:$A$116</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Deal Analyzer'!$B$105:$B$116</c:f>
-              <c:numCache>
-                <c:formatCode>$#,##0.00</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1400</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:sm="sm" uri="sm">
-              <sm:meanLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:meanLine>
-              <sm:minMaxLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:minMaxLine>
-              <sm:stDevLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:stDevLine>
-              <sm:trendLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:trendLine>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>After-Debt Cash Flow</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t">
-                <a:rot lat="0" lon="0" rev="12000000"/>
-              </a:lightRig>
-            </a:scene3d>
-            <a:sp3d prstMaterial="warmMatte"/>
-          </c:spPr>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Deal Analyzer'!$A$105:$A$116</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Deal Analyzer'!$F$105:$F$116</c:f>
-              <c:numCache>
-                <c:formatCode>$#,##0.00</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>-1213.38960077826</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1213.38960077826</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-1213.38960077826</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>186.610399221741</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:sm="sm" uri="sm">
-              <sm:meanLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:meanLine>
-              <sm:minMaxLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:minMaxLine>
-              <sm:stDevLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:stDevLine>
-              <sm:trendLine>
-                <c:spPr>
-                  <a:ln w="9525">
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-              </sm:trendLine>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
-        </c:dLbls>
-        <c:axId val="10"/>
-        <c:axId val="11"/>
-      </c:bar3DChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="11"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="l"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="11"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="r"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:ln w="9525">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr numCol="2"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr/>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
-  <c:spPr>
-    <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-    </a:ln>
-    <a:scene3d>
-      <a:camera prst="orthographicFront"/>
-      <a:lightRig rig="threePt" dir="t"/>
-    </a:scene3d>
-    <a:sp3d/>
-  </c:spPr>
+  <c:spPr/>
   <c:txPr>
-    <a:bodyPr anchor="t" rot="0"/>
+    <a:bodyPr anchor="ctr" anchorCtr="1" rot="0"/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
@@ -2597,14 +2516,104 @@
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
-          <a:latin typeface="Calibri" charset="0"/>
+          <a:latin typeface="Arial" charset="0"/>
         </a:defRPr>
       </a:pPr>
     </a:p>
   </c:txPr>
   <c:extLst>
     <c:ext xmlns:sm="sm" uri="sm">
-      <sm:colorScheme xmlns:sm="sm" id="1775267756" val="15"/>
+      <sm:colorScheme xmlns:sm="sm" id="1775607099" val="15"/>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr/>
+  <c:txPr>
+    <a:bodyPr anchor="ctr" anchorCtr="1" rot="0"/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-us" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="100">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:latin typeface="Arial" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:extLst>
+    <c:ext xmlns:sm="sm" uri="sm">
+      <sm:colorScheme xmlns:sm="sm" id="1775607099" val="15"/>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr/>
+  <c:txPr>
+    <a:bodyPr anchor="ctr" anchorCtr="1" rot="0"/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-us" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="100">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:latin typeface="Arial" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:extLst>
+    <c:ext xmlns:sm="sm" uri="sm">
+      <sm:colorScheme xmlns:sm="sm" id="1775607099" val="15"/>
     </c:ext>
   </c:extLst>
 </c:chartSpace>
@@ -2614,20 +2623,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvPr id="4" name="12-month: rent vs cash flow"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2637,6 +2646,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="12-month: rent allocation"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="6-year projection"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,8 +2969,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="smNativeData" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q117"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S120"/>
   <sheetFormatPr defaultRowHeight="15.40"/>
   <cols>
     <col min="1" max="1" width="6.000000" customWidth="1" style="6"/>
@@ -2926,14 +2995,6 @@
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="9"/>
       <c r="L1" s="9"/>
@@ -2944,17 +3005,17 @@
       <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:17" ht="22" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
       <c r="J2" s="8"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -2987,14 +3048,6 @@
       <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
       <c r="J4" s="8"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -3011,7 +3064,7 @@
       <c r="B5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="71" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -3038,7 +3091,7 @@
       <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="76" t="n">
+      <c r="C6" s="72" t="n">
         <v>85000</v>
       </c>
       <c r="D6" s="8"/>
@@ -3063,7 +3116,7 @@
       <c r="B7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="76" t="n">
+      <c r="C7" s="72" t="n">
         <v>69140</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -3090,7 +3143,7 @@
       <c r="B8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="76" t="n">
+      <c r="C8" s="72" t="n">
         <v>1700</v>
       </c>
       <c r="D8" s="8"/>
@@ -3113,7 +3166,7 @@
       <c r="B9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="73">
         <f>C8/C6</f>
         <v>0.02</v>
       </c>
@@ -3139,7 +3192,7 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="78" t="n">
+      <c r="C10" s="74" t="n">
         <v>7.5</v>
       </c>
       <c r="D10" s="8"/>
@@ -3164,7 +3217,7 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="78" t="n">
+      <c r="C11" s="74" t="n">
         <v>20</v>
       </c>
       <c r="D11" s="8"/>
@@ -3187,7 +3240,7 @@
       <c r="B12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="79" t="n">
+      <c r="C12" s="75" t="n">
         <v>50000</v>
       </c>
       <c r="D12" s="8"/>
@@ -3210,7 +3263,7 @@
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="81">
         <f>C6+C19+C20-C12-C14+C8</f>
         <v>26189.9860000000008</v>
       </c>
@@ -3245,7 +3298,7 @@
       <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="76" t="n">
+      <c r="C14" s="72" t="n">
         <v>15000</v>
       </c>
       <c r="D14" s="10" t="s">
@@ -3271,7 +3324,7 @@
       <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="76" t="n">
+      <c r="C15" s="72" t="n">
         <v>10</v>
       </c>
       <c r="D15" s="8"/>
@@ -3285,7 +3338,6 @@
       <c r="G15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
       <c r="K15" s="9"/>
@@ -3303,7 +3355,7 @@
       <c r="B16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="80" t="n">
+      <c r="C16" s="76" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="8"/>
@@ -3344,14 +3396,6 @@
       <c r="A18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -3368,7 +3412,7 @@
       <c r="B19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="76">
+      <c r="C19" s="72">
         <f>(C25+C24)/12*9</f>
         <v>1096.9860000000001</v>
       </c>
@@ -3398,14 +3442,14 @@
       <c r="B20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="76" t="n">
+      <c r="C20" s="72" t="n">
         <v>3393</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -3441,16 +3485,8 @@
     </row>
     <row r="22" spans="1:17" ht="22" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
+        <v>31</v>
+      </c>
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -3465,13 +3501,13 @@
         <v>12</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="81" t="n">
+        <v>32</v>
+      </c>
+      <c r="C23" s="77" t="n">
         <v>1.32000000000000006</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -3490,9 +3526,9 @@
     <row r="24" spans="1:17" ht="15" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="79">
+        <v>34</v>
+      </c>
+      <c r="C24" s="75">
         <f>C7*(C23/100)</f>
         <v>912.648000000000025</v>
       </c>
@@ -3516,9 +3552,9 @@
         <v>13</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="76" t="n">
+        <v>35</v>
+      </c>
+      <c r="C25" s="72" t="n">
         <v>550</v>
       </c>
       <c r="D25" s="8"/>
@@ -3541,10 +3577,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="76" t="n">
-        <v>370</v>
+        <v>36</v>
+      </c>
+      <c r="C26" s="72" t="n">
+        <v>500</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -3564,11 +3600,11 @@
     <row r="27" spans="1:17" ht="15" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="86">
+        <v>37</v>
+      </c>
+      <c r="C27" s="82">
         <f>C26*12</f>
-        <v>4440</v>
+        <v>6000</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -3606,16 +3642,8 @@
     </row>
     <row r="29" spans="1:17" ht="22" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
+        <v>38</v>
+      </c>
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -3630,9 +3658,9 @@
         <v>15</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="76" t="n">
+        <v>39</v>
+      </c>
+      <c r="C30" s="72" t="n">
         <v>1400</v>
       </c>
       <c r="D30" s="8"/>
@@ -3655,13 +3683,13 @@
         <v>16</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="82" t="n">
+        <v>40</v>
+      </c>
+      <c r="C31" s="78" t="n">
         <v>0.02</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -3682,9 +3710,9 @@
         <v>17</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="82" t="n">
+        <v>42</v>
+      </c>
+      <c r="C32" s="78" t="n">
         <v>0.03</v>
       </c>
       <c r="D32" s="8"/>
@@ -3707,9 +3735,9 @@
         <v>18</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="82" t="n">
+        <v>43</v>
+      </c>
+      <c r="C33" s="78" t="n">
         <v>0.02</v>
       </c>
       <c r="D33" s="8"/>
@@ -3748,16 +3776,8 @@
     </row>
     <row r="35" spans="1:17" ht="22" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
+        <v>44</v>
+      </c>
       <c r="J35" s="8"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
@@ -3772,9 +3792,9 @@
         <v>19</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="75" t="n">
+        <v>45</v>
+      </c>
+      <c r="C36" s="71" t="n">
         <v>3</v>
       </c>
       <c r="D36" s="8"/>
@@ -3797,13 +3817,13 @@
         <v>20</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="76" t="n">
+        <v>46</v>
+      </c>
+      <c r="C37" s="72" t="n">
         <v>15000</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -3824,13 +3844,13 @@
         <v>21</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="83" t="n">
+        <v>48</v>
+      </c>
+      <c r="C38" s="79" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -3848,16 +3868,8 @@
     </row>
     <row r="39" spans="1:17" ht="15" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
+        <v>50</v>
+      </c>
       <c r="J39" s="8"/>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
@@ -3872,9 +3884,9 @@
         <v>22</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="84" t="n">
+        <v>51</v>
+      </c>
+      <c r="C40" s="80" t="n">
         <v>0.25</v>
       </c>
       <c r="D40" s="8"/>
@@ -3897,13 +3909,13 @@
         <v>23</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="82" t="n">
+        <v>52</v>
+      </c>
+      <c r="C41" s="78" t="n">
         <v>0.2</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -3940,18 +3952,10 @@
     </row>
     <row r="43" spans="1:17" ht="22" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
+        <v>54</v>
+      </c>
       <c r="J43" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
@@ -3961,136 +3965,121 @@
       <c r="P43" s="16"/>
       <c r="Q43" s="16"/>
     </row>
-    <row r="44" spans="1:17" ht="21.75" customHeight="1">
+    <row r="44" spans="1:12" ht="21.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="66">
+        <v>56</v>
+      </c>
+      <c r="C44" s="62">
         <f>IF(C11&gt;0,-PMT(C10/100/12,C11*12,C12),0)</f>
         <v>402.79659677590098</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="O44"/>
-      <c r="P44"/>
-      <c r="Q44"/>
-    </row>
-    <row r="45" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="45" spans="1:12" ht="21.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="67">
+        <v>63</v>
+      </c>
+      <c r="C45" s="63">
         <f>IF(AND(C14&gt;0,C16&gt;0,C15&gt;0),-PMT(C15/100/12,C16*12,C14),0)</f>
         <v>318.705670669024983</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="54">
+        <v>64</v>
+      </c>
+      <c r="F45" s="52">
         <f>C52</f>
-        <v>24830.1548023348005</v>
+        <v>25220.1548023348005</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" s="51" t="s">
-        <v>62</v>
+        <v>65</v>
+      </c>
+      <c r="H45" s="50" t="s">
+        <v>66</v>
       </c>
       <c r="I45" s="20">
         <f>C59</f>
-        <v>0.111733552941176995</v>
+        <v>0.0933806117647059963</v>
       </c>
       <c r="J45" s="19"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
-    </row>
-    <row r="46" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="46" spans="1:12" ht="21.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="67">
+        <v>67</v>
+      </c>
+      <c r="C46" s="63">
         <f>C24/12</f>
         <v>76.054000000000002</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="54">
+        <v>68</v>
+      </c>
+      <c r="F46" s="52">
         <f>C58</f>
-        <v>9497.35200000000077</v>
+        <v>7937.35199999999986</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="H46" s="51" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="H46" s="50" t="s">
+        <v>70</v>
       </c>
       <c r="I46" s="20">
         <f>C60</f>
-        <v>0.0338026402711740026</v>
+        <v>-0.0285753681921250013</v>
       </c>
       <c r="J46" s="19"/>
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
-      <c r="P46"/>
-      <c r="Q46"/>
-    </row>
-    <row r="47" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="47" spans="1:12" ht="21.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="67">
+        <v>71</v>
+      </c>
+      <c r="C47" s="63">
         <f>C25/12</f>
         <v>45.8333333333333002</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F47" s="21">
         <f>C63</f>
-        <v>1.09694180560618992</v>
+        <v>0.916762191673208982</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" s="51" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="H47" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="I47" s="20">
         <f>C64</f>
@@ -4099,270 +4088,212 @@
       <c r="J47" s="19"/>
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="O47"/>
-      <c r="P47"/>
-      <c r="Q47"/>
-    </row>
-    <row r="48" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="48" spans="1:12" ht="21.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="67">
+        <v>75</v>
+      </c>
+      <c r="C48" s="63">
         <f>C44+C45+C46+C47+C26</f>
-        <v>1213.38960077826005</v>
+        <v>1343.38960077826005</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F48" s="63">
+        <v>76</v>
+      </c>
+      <c r="F48" s="59">
         <f>C62</f>
         <v>0.0164705882352940014</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H48" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="I48" s="64">
+        <v>77</v>
+      </c>
+      <c r="H48" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="I48" s="60">
         <f>C70</f>
-        <v>99943.878713842103</v>
+        <v>83806.7016571643035</v>
       </c>
       <c r="J48" s="19"/>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="O48"/>
-      <c r="P48"/>
-      <c r="Q48"/>
-    </row>
-    <row r="49" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="49" spans="1:12" ht="21.75" customHeight="1">
       <c r="A49" s="23"/>
       <c r="B49" s="23"/>
       <c r="C49" s="45"/>
       <c r="D49" s="23"/>
       <c r="E49" s="44" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F49" s="21">
         <f>D87</f>
-        <v>-163.389600778258995</v>
+        <v>-293.389600778259023</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="H49" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="I49" s="54">
+        <v>80</v>
+      </c>
+      <c r="H49" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="I49" s="52">
         <f>D92</f>
-        <v>1.70707454545454995</v>
+        <v>5.60707454545454986</v>
       </c>
       <c r="J49" s="19"/>
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
-      <c r="M49"/>
-      <c r="N49"/>
-      <c r="O49"/>
-      <c r="P49"/>
-      <c r="Q49"/>
-    </row>
-    <row r="50" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="50" spans="1:12" ht="21.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="67">
+        <v>82</v>
+      </c>
+      <c r="C50" s="63">
         <f>SUM(C8,C19,C20,C37)</f>
         <v>21189.9860000000008</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F50" s="21">
         <f>C37</f>
         <v>15000</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H50" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="I50" s="65">
+        <v>84</v>
+      </c>
+      <c r="H50" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="I50" s="61">
         <f>C38</f>
         <v>1</v>
       </c>
       <c r="J50" s="19"/>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
-      <c r="M50"/>
-      <c r="N50"/>
-      <c r="O50"/>
-      <c r="P50"/>
-      <c r="Q50"/>
-    </row>
-    <row r="51" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="51" spans="1:12" ht="21.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="67">
+        <v>86</v>
+      </c>
+      <c r="C51" s="63">
         <f>C48*C36</f>
-        <v>3640.16880233478014</v>
+        <v>4030.16880233478014</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="55"/>
+      <c r="F51" s="53"/>
       <c r="G51" s="9"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="57"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="54"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
-      <c r="M51"/>
-      <c r="N51"/>
-      <c r="O51"/>
-      <c r="P51"/>
-      <c r="Q51"/>
-    </row>
-    <row r="52" spans="1:17" ht="21.75" customHeight="1">
+    </row>
+    <row r="52" spans="1:12" ht="21.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="67">
+        <v>87</v>
+      </c>
+      <c r="C52" s="63">
         <f>C50+C51</f>
-        <v>24830.1548023348005</v>
+        <v>25220.1548023348005</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="F52" s="56"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="53"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="25"/>
-      <c r="K52" s="25"/>
-      <c r="L52" s="25"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
-      <c r="P52"/>
-      <c r="Q52"/>
-    </row>
-    <row r="53" spans="1:17" ht="21.75" customHeight="1">
+        <v>88</v>
+      </c>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="84"/>
+    </row>
+    <row r="53" spans="1:12" ht="21.75" customHeight="1">
       <c r="A53" s="23"/>
       <c r="B53" s="23"/>
       <c r="C53" s="24"/>
       <c r="D53" s="23"/>
       <c r="E53" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="O53"/>
-      <c r="P53"/>
-      <c r="Q53"/>
-    </row>
-    <row r="54" spans="1:17" ht="21.75" customHeight="1">
+        <v>89</v>
+      </c>
+      <c r="F53" s="83"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="83"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="84"/>
+    </row>
+    <row r="54" spans="1:12" ht="21.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="68">
+        <v>90</v>
+      </c>
+      <c r="C54" s="64">
         <f>((C6*(1-C41/100))+C37)/27.5</f>
         <v>3630.18181818181984</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54"/>
-    </row>
-    <row r="55" spans="1:17" ht="21.75" customHeight="1">
+        <v>91</v>
+      </c>
+      <c r="F54" s="83"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="83"/>
+      <c r="J54" s="83"/>
+      <c r="K54" s="83"/>
+      <c r="L54" s="84"/>
+    </row>
+    <row r="55" spans="1:12" ht="21.75" customHeight="1">
       <c r="A55" s="8"/>
       <c r="B55" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="68">
+        <v>92</v>
+      </c>
+      <c r="C55" s="64">
         <f>C30*(12-C38)</f>
         <v>15400</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55"/>
-    </row>
-    <row r="56" spans="1:17" ht="21.75" customHeight="1">
+        <v>94</v>
+      </c>
+      <c r="F55" s="83"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="83"/>
+      <c r="J55" s="83"/>
+      <c r="K55" s="83"/>
+      <c r="L55" s="84"/>
+    </row>
+    <row r="56" spans="1:4" ht="21.75" customHeight="1">
       <c r="A56" s="8"/>
       <c r="B56" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" s="69">
+        <v>95</v>
+      </c>
+      <c r="C56" s="65">
         <f>C30*12</f>
         <v>16800</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="M56"/>
-      <c r="N56"/>
-      <c r="O56"/>
-      <c r="P56"/>
-      <c r="Q56"/>
-    </row>
-    <row r="57" spans="1:17" ht="21.75" customHeight="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="21.75" customHeight="1">
       <c r="A57" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
+        <v>97</v>
+      </c>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
       <c r="L57" s="11"/>
@@ -4371,18 +4302,21 @@
       <c r="O57" s="11"/>
       <c r="P57" s="11"/>
       <c r="Q57" s="11"/>
-    </row>
-    <row r="58" spans="1:17" ht="22" customHeight="1">
+      <c r="R57" s="85" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="22" customHeight="1">
       <c r="A58" s="8"/>
       <c r="B58" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="67">
+        <v>99</v>
+      </c>
+      <c r="C58" s="63">
         <f>C55-(C24+C25+C27)</f>
-        <v>9497.35200000000077</v>
+        <v>7937.35199999999986</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -4397,18 +4331,25 @@
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
-    </row>
-    <row r="59" spans="1:17" ht="21.75" customHeight="1">
+      <c r="R58" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="S58">
+        <f>12*(C44+C45)</f>
+        <v>8658.02720933911041</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="21.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="70">
+        <v>102</v>
+      </c>
+      <c r="C59" s="66">
         <f>C58/C6</f>
-        <v>0.111733552941176995</v>
+        <v>0.0933806117647059963</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -4423,18 +4364,25 @@
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
-    </row>
-    <row r="60" spans="1:17" ht="21.75" customHeight="1">
+      <c r="R59" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="S59">
+        <f>IF(C44&gt;0,C58/(C44*12),"")</f>
+        <v>1.64213403314329014</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="21.75" customHeight="1">
       <c r="A60" s="8"/>
       <c r="B60" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" s="70">
+        <v>105</v>
+      </c>
+      <c r="C60" s="66">
         <f>(C58-((C44+C45)*12))/C52</f>
-        <v>0.0338026402711740026</v>
+        <v>-0.0285753681921250013</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -4449,18 +4397,25 @@
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
-    </row>
-    <row r="61" spans="1:17" ht="15" customHeight="1">
+      <c r="R60" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="S60">
+        <f>IF(D86&lt;&gt;0,D82/D86,"")</f>
+        <v>0.593362884614005015</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="70">
+        <v>108</v>
+      </c>
+      <c r="C61" s="66">
         <f>C6/C55</f>
         <v>5.51948051948051965</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -4475,18 +4430,25 @@
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
-    </row>
-    <row r="62" spans="1:17" ht="15" customHeight="1">
+      <c r="R61" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="S61" s="87">
+        <f>C63-1.25</f>
+        <v>-0.333237808326791018</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15" customHeight="1">
       <c r="A62" s="8"/>
       <c r="B62" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="70">
+        <v>111</v>
+      </c>
+      <c r="C62" s="66">
         <f>C30/C6</f>
         <v>0.0164705882352940014</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
@@ -4501,18 +4463,25 @@
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
+      <c r="R62" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="S62" t="str">
+        <f>IF(C63&gt;=1.25,"Yes","No")</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63" s="70">
+        <v>114</v>
+      </c>
+      <c r="C63" s="66">
         <f>C58/((C44+C45)*12)</f>
-        <v>1.09694180560618992</v>
+        <v>0.916762191673208982</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
@@ -4528,17 +4497,17 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
     </row>
-    <row r="64" spans="1:17" ht="15" customHeight="1">
+    <row r="64" spans="1:18" ht="15" customHeight="1">
       <c r="A64" s="8"/>
       <c r="B64" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="70">
+        <v>116</v>
+      </c>
+      <c r="C64" s="66">
         <f>C12/C6</f>
         <v>0.588235294117646923</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -4553,18 +4522,21 @@
       <c r="O64" s="9"/>
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
-    </row>
-    <row r="65" spans="1:17" ht="15" customHeight="1">
+      <c r="R64" s="85" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="15" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" s="70">
+        <v>119</v>
+      </c>
+      <c r="C65" s="66">
         <f>(C24+C25+C27)/C55</f>
-        <v>0.383288831168830981</v>
+        <v>0.484587532467532967</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
@@ -4579,11 +4551,18 @@
       <c r="O65" s="9"/>
       <c r="P65" s="9"/>
       <c r="Q65" s="9"/>
-    </row>
-    <row r="66" spans="1:17" ht="15" customHeight="1">
+      <c r="R65" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="S65">
+        <f>C24+C25+C27</f>
+        <v>7462.64800000000014</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="15" customHeight="1">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
-      <c r="C66" s="50"/>
+      <c r="C66" s="49"/>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -4598,19 +4577,18 @@
       <c r="O66" s="9"/>
       <c r="P66" s="9"/>
       <c r="Q66" s="9"/>
-    </row>
-    <row r="67" spans="1:17" ht="15" customHeight="1">
+      <c r="R66" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="S66">
+        <f>12*(C44+C45)</f>
+        <v>8658.02720933911041</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="15" customHeight="1">
       <c r="A67" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="46"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11"/>
+        <v>123</v>
+      </c>
       <c r="J67" s="11"/>
       <c r="K67" s="11"/>
       <c r="L67" s="11"/>
@@ -4619,18 +4597,25 @@
       <c r="O67" s="11"/>
       <c r="P67" s="11"/>
       <c r="Q67" s="11"/>
+      <c r="R67" s="86" t="s">
+        <v>124</v>
+      </c>
+      <c r="S67">
+        <f>C58-$S$66</f>
+        <v>-720.675209339111007</v>
+      </c>
     </row>
     <row r="68" spans="1:17" ht="22" customHeight="1">
       <c r="A68" s="8"/>
       <c r="B68" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C68" s="67">
+        <v>125</v>
+      </c>
+      <c r="C68" s="63">
         <f>MAX(C58/12,0)</f>
-        <v>791.446000000000026</v>
+        <v>661.446000000000026</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
@@ -4649,14 +4634,14 @@
     <row r="69" spans="1:17" ht="15" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C69" s="67">
+        <v>127</v>
+      </c>
+      <c r="C69" s="63">
         <f>IF(C10&gt;0,PV(C10/100/12,C11*12,-C68),0)</f>
-        <v>98243.878713842103</v>
+        <v>82106.7016571643035</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
@@ -4675,14 +4660,14 @@
     <row r="70" spans="1:17" ht="15" customHeight="1">
       <c r="A70" s="8"/>
       <c r="B70" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" s="67">
+        <v>129</v>
+      </c>
+      <c r="C70" s="63">
         <f>C69+C8</f>
-        <v>99943.878713842103</v>
+        <v>83806.7016571643035</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
@@ -4701,14 +4686,14 @@
     <row r="71" spans="1:17" ht="15" customHeight="1">
       <c r="A71" s="8"/>
       <c r="B71" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C71" s="67">
+        <v>131</v>
+      </c>
+      <c r="C71" s="63">
         <f>1-(C6/C70)</f>
-        <v>0.149522701201432984</v>
+        <v>-0.0142386983288899982</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
@@ -4727,7 +4712,7 @@
     <row r="72" spans="1:17" ht="15" customHeight="1">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
-      <c r="C72" s="47"/>
+      <c r="C72" s="46"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
@@ -4745,16 +4730,8 @@
     </row>
     <row r="73" spans="1:17" ht="22" customHeight="1">
       <c r="A73" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
+        <v>133</v>
+      </c>
       <c r="J73" s="11"/>
       <c r="K73" s="11"/>
       <c r="L73" s="11"/>
@@ -4769,25 +4746,25 @@
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="27" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G74" s="27" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H74" s="27" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I74" s="27" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J74" s="27" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
@@ -4800,34 +4777,34 @@
     <row r="75" spans="1:17" ht="19.50" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="28" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C75" s="8"/>
-      <c r="D75" s="71">
+      <c r="D75" s="67">
         <f>B117</f>
         <v>12600</v>
       </c>
-      <c r="E75" s="71">
+      <c r="E75" s="67">
         <f>C30*(1+C31/100)*12-C30*C38</f>
         <v>15403.3600000000006</v>
       </c>
-      <c r="F75" s="71">
+      <c r="F75" s="67">
         <f>E75*(1+C31/100)</f>
         <v>15406.4406720000006</v>
       </c>
-      <c r="G75" s="71">
+      <c r="G75" s="67">
         <f>F75*(1+C31/100)</f>
         <v>15409.5219601343997</v>
       </c>
-      <c r="H75" s="71">
+      <c r="H75" s="67">
         <f>G75*(1+C31/100)</f>
         <v>15412.6038645263998</v>
       </c>
-      <c r="I75" s="71">
+      <c r="I75" s="67">
         <f>H75*(1+C31/100)</f>
         <v>15415.6863852992992</v>
       </c>
-      <c r="J75" s="71">
+      <c r="J75" s="67">
         <f>SUM(D75:I75)</f>
         <v>89647.6128819600999</v>
       </c>
@@ -4842,34 +4819,34 @@
     <row r="76" spans="1:17" ht="19.50" customHeight="1">
       <c r="A76" s="8"/>
       <c r="B76" s="28" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C76" s="8"/>
-      <c r="D76" s="71">
+      <c r="D76" s="67">
         <f>C25</f>
         <v>550</v>
       </c>
-      <c r="E76" s="71">
+      <c r="E76" s="67">
         <f>D76*(1+C32/100)</f>
         <v>550.164999999999964</v>
       </c>
-      <c r="F76" s="71">
+      <c r="F76" s="67">
         <f>E76*(1+C32/100)</f>
         <v>550.330049499999973</v>
       </c>
-      <c r="G76" s="71">
+      <c r="G76" s="67">
         <f>F76*(1+C32/100)</f>
         <v>550.49514851485003</v>
       </c>
-      <c r="H76" s="71">
+      <c r="H76" s="67">
         <f>G76*(1+C32/100)</f>
         <v>550.660297059405025</v>
       </c>
-      <c r="I76" s="71">
+      <c r="I76" s="67">
         <f>H76*(1+C32/100)</f>
         <v>550.825495148523032</v>
       </c>
-      <c r="J76" s="71">
+      <c r="J76" s="67">
         <f>SUM(D76:I76)</f>
         <v>3302.47599022278018</v>
       </c>
@@ -4884,34 +4861,34 @@
     <row r="77" spans="1:17" ht="19.50" customHeight="1">
       <c r="A77" s="8"/>
       <c r="B77" s="28" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C77" s="8"/>
-      <c r="D77" s="71">
+      <c r="D77" s="67">
         <f>C24</f>
         <v>912.648000000000025</v>
       </c>
-      <c r="E77" s="71">
+      <c r="E77" s="67">
         <f>D77*(1+C32/100)</f>
         <v>912.921794399999953</v>
       </c>
-      <c r="F77" s="71">
+      <c r="F77" s="67">
         <f>E77*(1+C32/100)</f>
         <v>913.19567093831995</v>
       </c>
-      <c r="G77" s="71">
+      <c r="G77" s="67">
         <f>F77*(1+C32/100)</f>
         <v>913.469629639601976</v>
       </c>
-      <c r="H77" s="71">
+      <c r="H77" s="67">
         <f>G77*(1+C32/100)</f>
         <v>913.743670528494022</v>
       </c>
-      <c r="I77" s="71">
+      <c r="I77" s="67">
         <f>H77*(1+C32/100)</f>
         <v>914.017793629653056</v>
       </c>
-      <c r="J77" s="71">
+      <c r="J77" s="67">
         <f>SUM(D77:I77)</f>
         <v>5479.99655913606966</v>
       </c>
@@ -4926,36 +4903,36 @@
     <row r="78" spans="1:17" ht="19.50" customHeight="1">
       <c r="A78" s="8"/>
       <c r="B78" s="28" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C78" s="8"/>
-      <c r="D78" s="71">
+      <c r="D78" s="67">
         <f>C27</f>
-        <v>4440</v>
-      </c>
-      <c r="E78" s="71">
+        <v>6000</v>
+      </c>
+      <c r="E78" s="67">
         <f>D78*(1+C32/100)</f>
-        <v>4441.33200000000033</v>
-      </c>
-      <c r="F78" s="71">
+        <v>6001.80000000000018</v>
+      </c>
+      <c r="F78" s="67">
         <f>E78*(1+C32/100)</f>
-        <v>4442.66439960000025</v>
-      </c>
-      <c r="G78" s="71">
+        <v>6003.60054000000036</v>
+      </c>
+      <c r="G78" s="67">
         <f>F78*(1+C32/100)</f>
-        <v>4443.99719891988025</v>
-      </c>
-      <c r="H78" s="71">
+        <v>6005.40162016199974</v>
+      </c>
+      <c r="H78" s="67">
         <f>G78*(1+C32/100)</f>
-        <v>4445.33039807955993</v>
-      </c>
-      <c r="I78" s="71">
+        <v>6007.20324064805027</v>
+      </c>
+      <c r="I78" s="67">
         <f>H78*(1+C32/100)</f>
-        <v>4446.66399719897981</v>
-      </c>
-      <c r="J78" s="71">
+        <v>6009.00540162025027</v>
+      </c>
+      <c r="J78" s="67">
         <f>SUM(D78:I78)</f>
-        <v>26659.9879937984006</v>
+        <v>36027.0108024302972</v>
       </c>
       <c r="K78" s="9"/>
       <c r="L78" s="9"/>
@@ -4968,34 +4945,34 @@
     <row r="79" spans="1:17" ht="19.50" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="28" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C79" s="8"/>
-      <c r="D79" s="72">
+      <c r="D79" s="68">
         <f>C12*C10/100</f>
         <v>3750</v>
       </c>
-      <c r="E79" s="71">
+      <c r="E79" s="67">
         <f>D79*0.97</f>
         <v>3637.5</v>
       </c>
-      <c r="F79" s="71">
+      <c r="F79" s="67">
         <f>E79*0.97</f>
         <v>3528.375</v>
       </c>
-      <c r="G79" s="71">
+      <c r="G79" s="67">
         <f>F79*0.97</f>
         <v>3422.52374999999984</v>
       </c>
-      <c r="H79" s="71">
+      <c r="H79" s="67">
         <f>G79*0.97</f>
         <v>3319.84803749999992</v>
       </c>
-      <c r="I79" s="71">
+      <c r="I79" s="67">
         <f>H79*0.97</f>
         <v>3220.25259637499994</v>
       </c>
-      <c r="J79" s="71">
+      <c r="J79" s="67">
         <f>SUM(D79:I79)</f>
         <v>20878.4993838750015</v>
       </c>
@@ -5010,36 +4987,36 @@
     <row r="80" spans="1:17" ht="19.50" customHeight="1">
       <c r="A80" s="8"/>
       <c r="B80" s="28" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C80" s="8"/>
-      <c r="D80" s="71">
+      <c r="D80" s="67">
         <f>SUM(D76:D78)</f>
-        <v>5902.64800000000014</v>
-      </c>
-      <c r="E80" s="71">
+        <v>7462.64800000000014</v>
+      </c>
+      <c r="E80" s="67">
         <f>SUM(E76:E78)</f>
-        <v>5904.41879439999957</v>
-      </c>
-      <c r="F80" s="71">
+        <v>7464.88679440000033</v>
+      </c>
+      <c r="F80" s="67">
         <f>SUM(F76:F78)</f>
-        <v>5906.19012003831995</v>
-      </c>
-      <c r="G80" s="71">
+        <v>7467.12626043832006</v>
+      </c>
+      <c r="G80" s="67">
         <f>SUM(G76:G78)</f>
-        <v>5907.96197707433021</v>
-      </c>
-      <c r="H80" s="71">
+        <v>7469.3663983164497</v>
+      </c>
+      <c r="H80" s="67">
         <f>SUM(H76:H78)</f>
-        <v>5909.73436566746022</v>
-      </c>
-      <c r="I80" s="71">
+        <v>7471.60720823594966</v>
+      </c>
+      <c r="I80" s="67">
         <f>SUM(I76:I78)</f>
-        <v>5911.50728597715988</v>
-      </c>
-      <c r="J80" s="71">
+        <v>7473.84869039843034</v>
+      </c>
+      <c r="J80" s="67">
         <f>SUM(D80:I80)</f>
-        <v>35442.4605431573</v>
+        <v>44809.4833517891966</v>
       </c>
       <c r="K80" s="9"/>
       <c r="L80" s="9"/>
@@ -5053,13 +5030,13 @@
       <c r="A81" s="8"/>
       <c r="B81" s="28"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="71"/>
-      <c r="E81" s="71"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="71"/>
-      <c r="I81" s="71"/>
-      <c r="J81" s="71"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
+      <c r="H81" s="67"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="67"/>
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
       <c r="M81" s="9"/>
@@ -5071,36 +5048,36 @@
     <row r="82" spans="1:17" ht="19.50" customHeight="1">
       <c r="A82" s="8"/>
       <c r="B82" s="29" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C82" s="8"/>
-      <c r="D82" s="71">
+      <c r="D82" s="67">
         <f>D75-D80</f>
-        <v>6697.35199999999986</v>
-      </c>
-      <c r="E82" s="71">
+        <v>5137.35199999999986</v>
+      </c>
+      <c r="E82" s="67">
         <f>E75-E80</f>
-        <v>9498.9412056000001</v>
-      </c>
-      <c r="F82" s="71">
+        <v>7938.47320560000026</v>
+      </c>
+      <c r="F82" s="67">
         <f>F75-F80</f>
-        <v>9500.25055196168069</v>
-      </c>
-      <c r="G82" s="71">
+        <v>7939.31441156167966</v>
+      </c>
+      <c r="G82" s="67">
         <f>G75-G80</f>
-        <v>9501.5599830600695</v>
-      </c>
-      <c r="H82" s="71">
+        <v>7940.15556181795</v>
+      </c>
+      <c r="H82" s="67">
         <f>H75-H80</f>
-        <v>9502.86949885893955</v>
-      </c>
-      <c r="I82" s="71">
+        <v>7940.99665629045012</v>
+      </c>
+      <c r="I82" s="67">
         <f>I75-I80</f>
-        <v>9504.17909932214025</v>
-      </c>
-      <c r="J82" s="71">
+        <v>7941.83769490086979</v>
+      </c>
+      <c r="J82" s="67">
         <f>SUM(D82:I82)</f>
-        <v>54205.1523388027999</v>
+        <v>44838.1295301709979</v>
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
@@ -5113,34 +5090,34 @@
     <row r="83" spans="1:17" ht="19.50" customHeight="1">
       <c r="A83" s="8"/>
       <c r="B83" s="29" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C83" s="8"/>
-      <c r="D83" s="71">
+      <c r="D83" s="67">
         <f>D82/12</f>
-        <v>558.112666666666996</v>
-      </c>
-      <c r="E83" s="71">
+        <v>428.112666666666996</v>
+      </c>
+      <c r="E83" s="67">
         <f>E82/12</f>
-        <v>791.578433799999971</v>
-      </c>
-      <c r="F83" s="71">
+        <v>661.539433799999983</v>
+      </c>
+      <c r="F83" s="67">
         <f>F82/12</f>
-        <v>791.687545996806989</v>
-      </c>
-      <c r="G83" s="71">
+        <v>661.609534296807055</v>
+      </c>
+      <c r="G83" s="67">
         <f>G82/12</f>
-        <v>791.796665255006019</v>
-      </c>
-      <c r="H83" s="71">
+        <v>661.679630151495985</v>
+      </c>
+      <c r="H83" s="67">
         <f>H82/12</f>
-        <v>791.905791571577993</v>
-      </c>
-      <c r="I83" s="71">
+        <v>661.749721357537965</v>
+      </c>
+      <c r="I83" s="67">
         <f>I82/12</f>
-        <v>792.014924943512028</v>
-      </c>
-      <c r="J83" s="48"/>
+        <v>661.819807908406005</v>
+      </c>
+      <c r="J83" s="47"/>
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
       <c r="M83" s="9"/>
@@ -5152,34 +5129,34 @@
     <row r="84" spans="1:17" ht="19.50" customHeight="1">
       <c r="A84" s="8"/>
       <c r="B84" s="29" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C84" s="8"/>
-      <c r="D84" s="73">
+      <c r="D84" s="69">
         <f>D82/C52</f>
-        <v>0.269726550370529017</v>
-      </c>
-      <c r="E84" s="73">
+        <v>0.203700256412558023</v>
+      </c>
+      <c r="E84" s="69">
         <f>E82/C52</f>
-        <v>0.382556664717482988</v>
-      </c>
-      <c r="F84" s="73">
+        <v>0.314767029299324008</v>
+      </c>
+      <c r="F84" s="69">
         <f>F82/C52</f>
-        <v>0.382609396823750991</v>
-      </c>
-      <c r="G84" s="73">
+        <v>0.314800383811549001</v>
+      </c>
+      <c r="G84" s="69">
         <f>G82/C52</f>
-        <v>0.382662132342671981</v>
-      </c>
-      <c r="H84" s="73">
+        <v>0.314833736115009</v>
+      </c>
+      <c r="H84" s="69">
         <f>H82/C52</f>
-        <v>0.382714871272787036</v>
-      </c>
-      <c r="I84" s="73">
+        <v>0.314867086206596003</v>
+      </c>
+      <c r="I84" s="69">
         <f>I82/C52</f>
-        <v>0.382767613612641</v>
-      </c>
-      <c r="J84" s="48"/>
+        <v>0.314900434083206004</v>
+      </c>
+      <c r="J84" s="47"/>
       <c r="K84" s="9"/>
       <c r="L84" s="9"/>
       <c r="M84" s="9"/>
@@ -5192,13 +5169,13 @@
       <c r="A85" s="8"/>
       <c r="B85" s="29"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="71"/>
-      <c r="E85" s="71"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="71"/>
-      <c r="I85" s="71"/>
-      <c r="J85" s="48"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
+      <c r="H85" s="67"/>
+      <c r="I85" s="67"/>
+      <c r="J85" s="47"/>
       <c r="K85" s="9"/>
       <c r="L85" s="9"/>
       <c r="M85" s="9"/>
@@ -5210,34 +5187,34 @@
     <row r="86" spans="1:17" ht="32.70" customHeight="1">
       <c r="A86" s="8"/>
       <c r="B86" s="29" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C86" s="8"/>
-      <c r="D86" s="71">
+      <c r="D86" s="67">
         <f>12*(C44+C45)</f>
         <v>8658.02720933911041</v>
       </c>
-      <c r="E86" s="71">
+      <c r="E86" s="67">
         <f>D86</f>
         <v>8658.02720933911041</v>
       </c>
-      <c r="F86" s="71">
+      <c r="F86" s="67">
         <f>D86</f>
         <v>8658.02720933911041</v>
       </c>
-      <c r="G86" s="71">
+      <c r="G86" s="67">
         <f>D86</f>
         <v>8658.02720933911041</v>
       </c>
-      <c r="H86" s="71">
+      <c r="H86" s="67">
         <f>D86</f>
         <v>8658.02720933911041</v>
       </c>
-      <c r="I86" s="71">
+      <c r="I86" s="67">
         <f>D86</f>
         <v>8658.02720933911041</v>
       </c>
-      <c r="J86" s="48"/>
+      <c r="J86" s="47"/>
       <c r="K86" s="9"/>
       <c r="L86" s="9"/>
       <c r="M86" s="9"/>
@@ -5249,34 +5226,34 @@
     <row r="87" spans="1:17" ht="28.50" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="29" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C87" s="8"/>
-      <c r="D87" s="71">
+      <c r="D87" s="67">
         <f>(D82-D86)/12</f>
-        <v>-163.389600778258995</v>
-      </c>
-      <c r="E87" s="71">
+        <v>-293.389600778259023</v>
+      </c>
+      <c r="E87" s="67">
         <f>(E82-E86)/12</f>
-        <v>70.0761663550742071</v>
-      </c>
-      <c r="F87" s="71">
+        <v>-59.9628336449258015</v>
+      </c>
+      <c r="F87" s="67">
         <f>(F82-F86)/12</f>
-        <v>70.1852785518808986</v>
-      </c>
-      <c r="G87" s="71">
+        <v>-59.8927331481192979</v>
+      </c>
+      <c r="G87" s="67">
         <f>(G82-G86)/12</f>
-        <v>70.2943978100799001</v>
-      </c>
-      <c r="H87" s="71">
+        <v>-59.8226372934300983</v>
+      </c>
+      <c r="H87" s="67">
         <f>(H82-H86)/12</f>
-        <v>70.4035241266523997</v>
-      </c>
-      <c r="I87" s="71">
+        <v>-59.7525460873883034</v>
+      </c>
+      <c r="I87" s="67">
         <f>(I82-I86)/12</f>
-        <v>70.5126574985857957</v>
-      </c>
-      <c r="J87" s="48"/>
+        <v>-59.6824595365200992</v>
+      </c>
+      <c r="J87" s="47"/>
       <c r="K87" s="9"/>
       <c r="L87" s="9"/>
       <c r="M87" s="9"/>
@@ -5289,13 +5266,13 @@
       <c r="A88" s="8"/>
       <c r="B88" s="29"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="71"/>
-      <c r="E88" s="71"/>
-      <c r="F88" s="71"/>
-      <c r="G88" s="71"/>
-      <c r="H88" s="71"/>
-      <c r="I88" s="71"/>
-      <c r="J88" s="48"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
+      <c r="H88" s="67"/>
+      <c r="I88" s="67"/>
+      <c r="J88" s="47"/>
       <c r="K88" s="9"/>
       <c r="L88" s="9"/>
       <c r="M88" s="9"/>
@@ -5307,16 +5284,16 @@
     <row r="89" spans="1:17" ht="19.50" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C89" s="8"/>
-      <c r="D89" s="71"/>
-      <c r="E89" s="71"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="71"/>
-      <c r="H89" s="71"/>
-      <c r="I89" s="71"/>
-      <c r="J89" s="48"/>
+      <c r="D89" s="67"/>
+      <c r="E89" s="67"/>
+      <c r="F89" s="67"/>
+      <c r="G89" s="67"/>
+      <c r="H89" s="67"/>
+      <c r="I89" s="67"/>
+      <c r="J89" s="47"/>
       <c r="K89" s="9"/>
       <c r="L89" s="9"/>
       <c r="M89" s="9"/>
@@ -5328,34 +5305,34 @@
     <row r="90" spans="1:17" ht="19.50" customHeight="1">
       <c r="A90" s="8"/>
       <c r="B90" s="29" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C90" s="8"/>
-      <c r="D90" s="71">
+      <c r="D90" s="67">
         <f>C54</f>
         <v>3630.18181818181984</v>
       </c>
-      <c r="E90" s="71">
+      <c r="E90" s="67">
         <f>D90</f>
         <v>3630.18181818181984</v>
       </c>
-      <c r="F90" s="71">
+      <c r="F90" s="67">
         <f>D90</f>
         <v>3630.18181818181984</v>
       </c>
-      <c r="G90" s="71">
+      <c r="G90" s="67">
         <f>D90</f>
         <v>3630.18181818181984</v>
       </c>
-      <c r="H90" s="71">
+      <c r="H90" s="67">
         <f>D90</f>
         <v>3630.18181818181984</v>
       </c>
-      <c r="I90" s="71">
+      <c r="I90" s="67">
         <f>D90</f>
         <v>3630.18181818181984</v>
       </c>
-      <c r="J90" s="48"/>
+      <c r="J90" s="47"/>
       <c r="K90" s="9"/>
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
@@ -5367,34 +5344,34 @@
     <row r="91" spans="1:17" ht="19.50" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="29" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C91" s="8"/>
-      <c r="D91" s="71">
+      <c r="D91" s="67">
         <f>D82-D79-D90</f>
-        <v>-682.829818181819974</v>
-      </c>
-      <c r="E91" s="71">
+        <v>-2242.82981818181997</v>
+      </c>
+      <c r="E91" s="67">
         <f>E82-E79-E90</f>
-        <v>2231.25938741817981</v>
-      </c>
-      <c r="F91" s="71">
+        <v>670.791387418180989</v>
+      </c>
+      <c r="F91" s="67">
         <f>F82-F79-F90</f>
-        <v>2341.69373377985994</v>
-      </c>
-      <c r="G91" s="71">
+        <v>780.757593379860054</v>
+      </c>
+      <c r="G91" s="67">
         <f>G82-G79-G90</f>
-        <v>2448.85441487824983</v>
-      </c>
-      <c r="H91" s="71">
+        <v>887.449993636129989</v>
+      </c>
+      <c r="H91" s="67">
         <f>H82-H79-H90</f>
-        <v>2552.8396431771198</v>
-      </c>
-      <c r="I91" s="71">
+        <v>990.966800608630024</v>
+      </c>
+      <c r="I91" s="67">
         <f>I82-I79-I90</f>
-        <v>2653.74468476532002</v>
-      </c>
-      <c r="J91" s="48"/>
+        <v>1091.40328034405002</v>
+      </c>
+      <c r="J91" s="47"/>
       <c r="K91" s="9"/>
       <c r="L91" s="9"/>
       <c r="M91" s="9"/>
@@ -5406,34 +5383,34 @@
     <row r="92" spans="1:17" ht="19.50" customHeight="1">
       <c r="A92" s="8"/>
       <c r="B92" s="29" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="C92" s="8"/>
-      <c r="D92" s="71">
+      <c r="D92" s="67">
         <f>-D91*(C40/100)</f>
-        <v>1.70707454545454995</v>
-      </c>
-      <c r="E92" s="71">
+        <v>5.60707454545454986</v>
+      </c>
+      <c r="E92" s="67">
         <f>-E91*(C40/100)</f>
-        <v>-5.5781484685454501</v>
-      </c>
-      <c r="F92" s="71">
+        <v>-1.67697846854545007</v>
+      </c>
+      <c r="F92" s="67">
         <f>-F91*(C40/100)</f>
-        <v>-5.85423433444965013</v>
-      </c>
-      <c r="G92" s="71">
+        <v>-1.95189398344964999</v>
+      </c>
+      <c r="G92" s="67">
         <f>-G91*(C40/100)</f>
-        <v>-6.12213603719562993</v>
-      </c>
-      <c r="H92" s="71">
+        <v>-2.21862498409032982</v>
+      </c>
+      <c r="H92" s="67">
         <f>-H91*(C40/100)</f>
-        <v>-6.38209910794279978</v>
-      </c>
-      <c r="I92" s="71">
+        <v>-2.47741700152158018</v>
+      </c>
+      <c r="I92" s="67">
         <f>-I91*(C40/100)</f>
-        <v>-6.63436171191330004</v>
-      </c>
-      <c r="J92" s="48"/>
+        <v>-2.72850820086013002</v>
+      </c>
+      <c r="J92" s="47"/>
       <c r="K92" s="9"/>
       <c r="L92" s="9"/>
       <c r="M92" s="9"/>
@@ -5446,13 +5423,13 @@
       <c r="A93" s="8"/>
       <c r="B93" s="29"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="74"/>
-      <c r="E93" s="74"/>
-      <c r="F93" s="74"/>
-      <c r="G93" s="74"/>
-      <c r="H93" s="74"/>
-      <c r="I93" s="74"/>
-      <c r="J93" s="48"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="70"/>
+      <c r="I93" s="70"/>
+      <c r="J93" s="47"/>
       <c r="K93" s="9"/>
       <c r="L93" s="9"/>
       <c r="M93" s="9"/>
@@ -5464,16 +5441,16 @@
     <row r="94" spans="1:17" ht="19.50" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="29" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C94" s="8"/>
-      <c r="D94" s="71"/>
-      <c r="E94" s="71"/>
-      <c r="F94" s="71"/>
-      <c r="G94" s="71"/>
-      <c r="H94" s="71"/>
-      <c r="I94" s="71"/>
-      <c r="J94" s="48"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
+      <c r="H94" s="67"/>
+      <c r="I94" s="67"/>
+      <c r="J94" s="47"/>
       <c r="K94" s="9"/>
       <c r="L94" s="9"/>
       <c r="M94" s="9"/>
@@ -5485,34 +5462,34 @@
     <row r="95" spans="1:17" ht="19.50" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="29" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C95" s="8"/>
-      <c r="D95" s="71">
+      <c r="D95" s="67">
         <f>D87*12+D92</f>
-        <v>-1958.96813479366006</v>
-      </c>
-      <c r="E95" s="71">
+        <v>-3515.06813479366019</v>
+      </c>
+      <c r="E95" s="67">
         <f>E87*12+E92</f>
-        <v>835.335847792346044</v>
-      </c>
-      <c r="F95" s="71">
+        <v>-721.230982207655984</v>
+      </c>
+      <c r="F95" s="67">
         <f>F87*12+F92</f>
-        <v>836.36910828812097</v>
-      </c>
-      <c r="G95" s="71">
+        <v>-720.664691760881965</v>
+      </c>
+      <c r="G95" s="67">
         <f>G87*12+G92</f>
-        <v>837.410637683762957</v>
-      </c>
-      <c r="H95" s="71">
+        <v>-720.09027250525105</v>
+      </c>
+      <c r="H95" s="67">
         <f>H87*12+H92</f>
-        <v>838.460190411885947</v>
-      </c>
-      <c r="I95" s="71">
+        <v>-719.507970050182053</v>
+      </c>
+      <c r="I95" s="67">
         <f>I87*12+I92</f>
-        <v>839.517528271117044</v>
-      </c>
-      <c r="J95" s="59"/>
+        <v>-718.918022639100968</v>
+      </c>
+      <c r="J95" s="55"/>
       <c r="K95" s="9"/>
       <c r="L95" s="9"/>
       <c r="M95" s="9"/>
@@ -5524,34 +5501,34 @@
     <row r="96" spans="1:17" ht="19.50" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="29" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C96" s="8"/>
-      <c r="D96" s="71">
+      <c r="D96" s="67">
         <f>C6*(1+C33/100)</f>
         <v>85017</v>
       </c>
-      <c r="E96" s="71">
+      <c r="E96" s="67">
         <f>D96*(1+C33/100)</f>
         <v>85034.0034000000014</v>
       </c>
-      <c r="F96" s="71">
+      <c r="F96" s="67">
         <f>E96*(1+C33/100)</f>
         <v>85051.0102006800007</v>
       </c>
-      <c r="G96" s="71">
+      <c r="G96" s="67">
         <f>F96*(1+C33/100)</f>
         <v>85068.020402720198</v>
       </c>
-      <c r="H96" s="71">
+      <c r="H96" s="67">
         <f>G96*(1+C33/100)</f>
         <v>85085.0340068007063</v>
       </c>
-      <c r="I96" s="71">
+      <c r="I96" s="67">
         <f>H96*(1+C33/100)</f>
         <v>85102.0510136021039</v>
       </c>
-      <c r="J96" s="48"/>
+      <c r="J96" s="47"/>
       <c r="K96" s="9"/>
       <c r="L96" s="9"/>
       <c r="M96" s="9"/>
@@ -5563,34 +5540,34 @@
     <row r="97" spans="1:17" ht="19.50" customHeight="1">
       <c r="A97" s="8"/>
       <c r="B97" s="29" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C97" s="8"/>
-      <c r="D97" s="73">
+      <c r="D97" s="69">
         <f>D95/C52</f>
-        <v>-0.0788947209708680042</v>
-      </c>
-      <c r="E97" s="73">
+        <v>-0.139375359205497018</v>
+      </c>
+      <c r="E97" s="69">
         <f>E95/C52</f>
-        <v>0.0336419911370750002</v>
-      </c>
-      <c r="F97" s="73">
+        <v>-0.0285974050460980003</v>
+      </c>
+      <c r="F97" s="69">
         <f>F95/C52</f>
-        <v>0.0336836042685269987</v>
-      </c>
-      <c r="G97" s="73">
+        <v>-0.0285749511614479967</v>
+      </c>
+      <c r="G97" s="69">
         <f>G95/C52</f>
-        <v>0.0337255504184379973</v>
-      </c>
-      <c r="H97" s="73">
+        <v>-0.0285521749628030008</v>
+      </c>
+      <c r="H97" s="69">
         <f>H95/C52</f>
-        <v>0.0337678196969209976</v>
-      </c>
-      <c r="I97" s="73">
+        <v>-0.0285290861887800027</v>
+      </c>
+      <c r="I97" s="69">
         <f>I95/C52</f>
-        <v>0.0338104025107480055</v>
-      </c>
-      <c r="J97" s="48"/>
+        <v>-0.0285056942859269959</v>
+      </c>
+      <c r="J97" s="47"/>
       <c r="K97" s="9"/>
       <c r="L97" s="9"/>
       <c r="M97" s="9"/>
@@ -5603,13 +5580,13 @@
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="47"/>
-      <c r="E98" s="47"/>
-      <c r="F98" s="47"/>
-      <c r="G98" s="47"/>
-      <c r="H98" s="47"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="47"/>
+      <c r="D98" s="46"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="46"/>
+      <c r="G98" s="46"/>
+      <c r="H98" s="46"/>
+      <c r="I98" s="46"/>
+      <c r="J98" s="46"/>
       <c r="K98" s="9"/>
       <c r="L98" s="9"/>
       <c r="M98" s="9"/>
@@ -5622,13 +5599,13 @@
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="47"/>
-      <c r="I99" s="47"/>
-      <c r="J99" s="47"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="46"/>
+      <c r="F99" s="46"/>
+      <c r="G99" s="46"/>
+      <c r="H99" s="46"/>
+      <c r="I99" s="46"/>
+      <c r="J99" s="46"/>
       <c r="K99" s="9"/>
       <c r="L99" s="9"/>
       <c r="M99" s="9"/>
@@ -5640,7 +5617,7 @@
     <row r="100" spans="1:17" ht="19.50" customHeight="1">
       <c r="A100" s="8"/>
       <c r="B100" s="41" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C100" s="41"/>
       <c r="D100" s="41"/>
@@ -5698,7 +5675,7 @@
     </row>
     <row r="103" spans="1:17" ht="22" customHeight="1">
       <c r="A103" s="11" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
@@ -5718,26 +5695,26 @@
       <c r="Q103" s="11"/>
     </row>
     <row r="104" spans="1:17" ht="22" customHeight="1">
-      <c r="A104" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="B104" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="C104" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="D104" s="60" t="s">
-        <v>148</v>
-      </c>
-      <c r="E104" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="F104" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="G104" s="60" t="s">
-        <v>151</v>
+      <c r="A104" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="C104" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E104" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="F104" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="G104" s="56" t="s">
+        <v>168</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -5754,25 +5731,25 @@
       <c r="A105" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B105" s="49">
-        <f>IF(A105&lt;=$C$38,0,$C$30)</f>
+      <c r="B105" s="48">
+        <f>IF(A105&lt;=$C$36,0,$C$30)</f>
         <v>0</v>
       </c>
-      <c r="C105" s="49">
+      <c r="C105" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D105" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D105" s="48">
         <f>B105-C105</f>
-        <v>-491.887333333333004</v>
-      </c>
-      <c r="E105" s="49">
+        <v>-621.887333333333004</v>
+      </c>
+      <c r="E105" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F105" s="49">
+      <c r="F105" s="48">
         <f>D105-E105</f>
-        <v>-1213.38960077826005</v>
+        <v>-1343.38960077826005</v>
       </c>
       <c r="G105" s="30" t="str">
         <f>IF(B105=0,"Vacant / turn month","Occupied month")</f>
@@ -5793,25 +5770,25 @@
       <c r="A106" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B106" s="49">
+      <c r="B106" s="48">
         <f>IF(A106&lt;=$C$36,0,$C$30)</f>
         <v>0</v>
       </c>
-      <c r="C106" s="49">
+      <c r="C106" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D106" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D106" s="48">
         <f>B106-C106</f>
-        <v>-491.887333333333004</v>
-      </c>
-      <c r="E106" s="49">
+        <v>-621.887333333333004</v>
+      </c>
+      <c r="E106" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F106" s="49">
+      <c r="F106" s="48">
         <f>D106-E106</f>
-        <v>-1213.38960077826005</v>
+        <v>-1343.38960077826005</v>
       </c>
       <c r="G106" s="30" t="str">
         <f>IF(B106=0,"Vacant / turn month","Occupied month")</f>
@@ -5832,25 +5809,25 @@
       <c r="A107" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B107" s="49">
+      <c r="B107" s="48">
         <f>IF(A107&lt;=$C$36,0,$C$30)</f>
         <v>0</v>
       </c>
-      <c r="C107" s="49">
+      <c r="C107" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D107" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D107" s="48">
         <f>B107-C107</f>
-        <v>-491.887333333333004</v>
-      </c>
-      <c r="E107" s="49">
+        <v>-621.887333333333004</v>
+      </c>
+      <c r="E107" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F107" s="49">
+      <c r="F107" s="48">
         <f>D107-E107</f>
-        <v>-1213.38960077826005</v>
+        <v>-1343.38960077826005</v>
       </c>
       <c r="G107" s="30" t="str">
         <f>IF(B107=0,"Vacant / turn month","Occupied month")</f>
@@ -5871,25 +5848,25 @@
       <c r="A108" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B108" s="49">
+      <c r="B108" s="48">
         <f>IF(A108&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C108" s="49">
+      <c r="C108" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D108" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D108" s="48">
         <f>B108-C108</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E108" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E108" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F108" s="49">
+      <c r="F108" s="48">
         <f>D108-E108</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G108" s="30" t="str">
         <f>IF(B108=0,"Vacant / turn month","Occupied month")</f>
@@ -5910,25 +5887,25 @@
       <c r="A109" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B109" s="49">
+      <c r="B109" s="48">
         <f>IF(A109&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C109" s="49">
+      <c r="C109" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D109" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D109" s="48">
         <f>B109-C109</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E109" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E109" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F109" s="49">
+      <c r="F109" s="48">
         <f>D109-E109</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G109" s="30" t="str">
         <f>IF(B109=0,"Vacant / turn month","Occupied month")</f>
@@ -5949,25 +5926,25 @@
       <c r="A110" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B110" s="49">
+      <c r="B110" s="48">
         <f>IF(A110&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C110" s="49">
+      <c r="C110" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D110" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D110" s="48">
         <f>B110-C110</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E110" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E110" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F110" s="49">
+      <c r="F110" s="48">
         <f>D110-E110</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G110" s="30" t="str">
         <f>IF(B110=0,"Vacant / turn month","Occupied month")</f>
@@ -5988,25 +5965,25 @@
       <c r="A111" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B111" s="49">
+      <c r="B111" s="48">
         <f>IF(A111&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C111" s="49">
+      <c r="C111" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D111" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D111" s="48">
         <f>B111-C111</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E111" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E111" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F111" s="49">
+      <c r="F111" s="48">
         <f>D111-E111</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G111" s="30" t="str">
         <f>IF(B111=0,"Vacant / turn month","Occupied month")</f>
@@ -6027,25 +6004,25 @@
       <c r="A112" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B112" s="49">
+      <c r="B112" s="48">
         <f>IF(A112&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C112" s="49">
+      <c r="C112" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D112" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D112" s="48">
         <f>B112-C112</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E112" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E112" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F112" s="49">
+      <c r="F112" s="48">
         <f>D112-E112</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G112" s="30" t="str">
         <f>IF(B112=0,"Vacant / turn month","Occupied month")</f>
@@ -6066,25 +6043,25 @@
       <c r="A113" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B113" s="49">
+      <c r="B113" s="48">
         <f>IF(A113&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C113" s="49">
+      <c r="C113" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D113" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D113" s="48">
         <f>B113-C113</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E113" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E113" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F113" s="49">
+      <c r="F113" s="48">
         <f>D113-E113</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G113" s="30" t="str">
         <f>IF(B113=0,"Vacant / turn month","Occupied month")</f>
@@ -6105,25 +6082,25 @@
       <c r="A114" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B114" s="49">
+      <c r="B114" s="48">
         <f>IF(A114&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C114" s="49">
+      <c r="C114" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D114" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D114" s="48">
         <f>B114-C114</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E114" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E114" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F114" s="49">
+      <c r="F114" s="48">
         <f>D114-E114</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G114" s="30" t="str">
         <f>IF(B114=0,"Vacant / turn month","Occupied month")</f>
@@ -6144,25 +6121,25 @@
       <c r="A115" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B115" s="49">
+      <c r="B115" s="48">
         <f>IF(A115&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C115" s="49">
+      <c r="C115" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D115" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D115" s="48">
         <f>B115-C115</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E115" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E115" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F115" s="49">
+      <c r="F115" s="48">
         <f>D115-E115</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G115" s="30" t="str">
         <f>IF(B115=0,"Vacant / turn month","Occupied month")</f>
@@ -6183,25 +6160,25 @@
       <c r="A116" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B116" s="49">
+      <c r="B116" s="48">
         <f>IF(A116&lt;=$C$36,0,$C$30)</f>
         <v>1400</v>
       </c>
-      <c r="C116" s="49">
+      <c r="C116" s="48">
         <f>($C$24+$C$25+$C$27)/12</f>
-        <v>491.887333333333004</v>
-      </c>
-      <c r="D116" s="49">
+        <v>621.887333333333004</v>
+      </c>
+      <c r="D116" s="48">
         <f>B116-C116</f>
-        <v>908.112666666666996</v>
-      </c>
-      <c r="E116" s="49">
+        <v>778.112666666666996</v>
+      </c>
+      <c r="E116" s="48">
         <f>$C$44+$C$45</f>
         <v>721.502267444926019</v>
       </c>
-      <c r="F116" s="49">
+      <c r="F116" s="48">
         <f>D116-E116</f>
-        <v>186.610399221741005</v>
+        <v>56.6103992217409981</v>
       </c>
       <c r="G116" s="30" t="str">
         <f>IF(B116=0,"Vacant / turn month","Occupied month")</f>
@@ -6219,30 +6196,30 @@
       <c r="Q116" s="9"/>
     </row>
     <row r="117" spans="1:17" ht="21" customHeight="1">
-      <c r="A117" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="B117" s="62">
+      <c r="A117" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="B117" s="58">
         <f>SUM(B105:B116)</f>
         <v>12600</v>
       </c>
-      <c r="C117" s="62">
+      <c r="C117" s="58">
         <f>SUM(C105:C116)</f>
-        <v>5902.64800000000014</v>
-      </c>
-      <c r="D117" s="62">
+        <v>7462.64800000000014</v>
+      </c>
+      <c r="D117" s="58">
         <f>SUM(D105:D116)</f>
-        <v>6697.35199999999986</v>
-      </c>
-      <c r="E117" s="62">
+        <v>5137.35199999999986</v>
+      </c>
+      <c r="E117" s="58">
         <f>SUM(E105:E116)</f>
         <v>8658.02720933911951</v>
       </c>
-      <c r="F117" s="62">
+      <c r="F117" s="58">
         <f>SUM(F105:F116)</f>
-        <v>-1960.6752093391101</v>
-      </c>
-      <c r="G117" s="61"/>
+        <v>-3520.6752093391101</v>
+      </c>
+      <c r="G117" s="57"/>
       <c r="H117" s="8"/>
       <c r="I117" s="8"/>
       <c r="J117" s="8"/>
@@ -6254,8 +6231,37 @@
       <c r="P117" s="9"/>
       <c r="Q117" s="9"/>
     </row>
+    <row r="120" spans="2:9">
+      <c r="B120" t="s">
+        <v>170</v>
+      </c>
+      <c r="D120">
+        <f>D76+D77</f>
+        <v>1462.64799999999991</v>
+      </c>
+      <c r="E120">
+        <f>E76+E77</f>
+        <v>1463.08679439999992</v>
+      </c>
+      <c r="F120">
+        <f>F76+F77</f>
+        <v>1463.52572043831992</v>
+      </c>
+      <c r="G120">
+        <f>G76+G77</f>
+        <v>1463.96477815444996</v>
+      </c>
+      <c r="H120">
+        <f>H76+H77</f>
+        <v>1464.40396758790007</v>
+      </c>
+      <c r="I120">
+        <f>I76+I77</f>
+        <v>1464.84328877818007</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection password="EAB8" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection password="EAB8" sheet="1" autoFilter="0"/>
   <mergeCells count="17">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -6275,10 +6281,40 @@
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A73:I73"/>
   </mergeCells>
+  <conditionalFormatting sqref="C63">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$C$63&gt;=1.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C63">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>AND($C$63&gt;=1,$C$63&lt;1.25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C63">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+      <formula>$C$63&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+      <formula>$F$47&gt;=1.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+      <formula>AND($F$47&gt;=1,$F$47&lt;1.25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
+      <formula>$F$47&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <ns1:pageFlags id="1775267756" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1775607099" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -6287,20 +6323,20 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <ns1:header id="1775267756" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <ns1:footer id="1775267756" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <ns1:paperBin id="1775267756" Id="0" type="0" value="0"/>
-        <ns1:paperBin id="1775267756" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1775607099" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1775607099" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775607099" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775607099" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <ns1:sheetPrefs day="1775267756" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
-        <ns1:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-        <ns1:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-      </ns1:sheetPrefs>
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775607099" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
     </ext>
   </extLst>
 </worksheet>
@@ -6318,27 +6354,19 @@
     <col min="5" max="5" width="12.000000" customWidth="1" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:1" ht="24" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-    </row>
-    <row r="2" spans="1:5" ht="33.75" customHeight="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="33.75" customHeight="1">
       <c r="A2" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
+        <v>172</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="33" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
@@ -6347,275 +6375,253 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="35">
-        <f>'Deal Analyzer'!C59</f>
-        <v>0.111733552941176995</v>
+        <v>174</v>
+      </c>
+      <c r="B5" s="35" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="35">
-        <f>'Deal Analyzer'!C60</f>
-        <v>0.0338026402711740026</v>
+        <v>178</v>
+      </c>
+      <c r="B6" s="35" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="36">
-        <f>'Deal Analyzer'!C63</f>
-        <v>1.09694180560618992</v>
+        <v>182</v>
+      </c>
+      <c r="B7" s="36" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="35">
-        <f>'Deal Analyzer'!C64</f>
-        <v>0.588235294117646923</v>
+        <v>186</v>
+      </c>
+      <c r="B8" s="35" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="37">
-        <f>'Deal Analyzer'!E87</f>
-        <v>70.0761663550742071</v>
+        <v>190</v>
+      </c>
+      <c r="B9" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="42" customHeight="1">
       <c r="A12" s="39" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="42" customHeight="1">
       <c r="A13" s="39" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="39" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="42" customHeight="1">
       <c r="A15" s="39" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="42" customHeight="1">
       <c r="A16" s="39" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="42" customHeight="1">
       <c r="A17" s="39" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="42" customHeight="1">
       <c r="A18" s="39" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="42" customHeight="1">
       <c r="A19" s="39" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15" customHeight="1">
       <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-    </row>
+    </row>
+    <row r="22" spans="1:1" ht="15" customHeight="1"/>
+    <row r="23" spans="1:1" ht="15" customHeight="1"/>
+    <row r="24" spans="1:1" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
@@ -6623,24 +6629,24 @@
     <mergeCell ref="A21:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="E12:E19">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>E12="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:E19">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>E12="Medium"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:E19">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>E12="Low"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1775267756" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1775607099" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -6649,16 +6655,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1775267756" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1775267756" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775267756" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775267756" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1775607099" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1775607099" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775607099" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775607099" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775267756" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775607099" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
